--- a/output/valuation_summary.xlsx
+++ b/output/valuation_summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,11 @@
           <t>div_yield</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -531,6 +536,11 @@
       <c r="M2" t="n">
         <v>0.96</v>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -580,6 +590,11 @@
       <c r="M3" t="n">
         <v>1.65</v>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -629,6 +644,11 @@
       <c r="M4" t="n">
         <v>0.83</v>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -678,6 +698,11 @@
       <c r="M5" t="n">
         <v>0.89</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -727,6 +752,11 @@
       <c r="M6" t="n">
         <v>1.16</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -776,6 +806,11 @@
       <c r="M7" t="n">
         <v>1.65</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -825,6 +860,11 @@
       <c r="M8" t="n">
         <v>3.1</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -874,6 +914,11 @@
       <c r="M9" t="n">
         <v>3.22</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -923,6 +968,11 @@
       <c r="M10" t="n">
         <v>2.42</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -972,6 +1022,11 @@
       <c r="M11" t="n">
         <v>0.51</v>
       </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1021,6 +1076,11 @@
       <c r="M12" t="n">
         <v>2.32</v>
       </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1070,6 +1130,11 @@
       <c r="M13" t="n">
         <v>3.59</v>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1119,6 +1184,11 @@
       <c r="M14" t="n">
         <v>2.56</v>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1168,6 +1238,11 @@
       <c r="M15" t="n">
         <v>3.37</v>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1217,6 +1292,11 @@
       <c r="M16" t="n">
         <v>0.27</v>
       </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1266,6 +1346,11 @@
       <c r="M17" t="n">
         <v>2.62</v>
       </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1315,6 +1400,11 @@
       <c r="M18" t="n">
         <v>0.76</v>
       </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1364,6 +1454,11 @@
       <c r="M19" t="n">
         <v>1.02</v>
       </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1413,6 +1508,11 @@
       <c r="M20" t="n">
         <v>4.04</v>
       </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1462,6 +1562,11 @@
       <c r="M21" t="n">
         <v>4.23</v>
       </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1511,6 +1616,11 @@
       <c r="M22" t="n">
         <v>1.15</v>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1560,6 +1670,11 @@
       <c r="M23" t="n">
         <v>1.88</v>
       </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1609,6 +1724,11 @@
       <c r="M24" t="n">
         <v>3.81</v>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1658,6 +1778,11 @@
       <c r="M25" t="n">
         <v>2.83</v>
       </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1707,6 +1832,11 @@
       <c r="M26" t="n">
         <v>0.12</v>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1756,6 +1886,11 @@
       <c r="M27" t="n">
         <v>4.38</v>
       </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1805,6 +1940,11 @@
       <c r="M28" t="n">
         <v>3.42</v>
       </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1854,6 +1994,11 @@
       <c r="M29" t="n">
         <v>1.39</v>
       </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1903,6 +2048,11 @@
       <c r="M30" t="n">
         <v>2.58</v>
       </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1952,6 +2102,11 @@
       <c r="M31" t="n">
         <v>1.94</v>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2001,6 +2156,11 @@
       <c r="M32" t="n">
         <v>0.09</v>
       </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2050,6 +2210,11 @@
       <c r="M33" t="n">
         <v>4.41</v>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2099,6 +2264,11 @@
       <c r="M34" t="n">
         <v>0.31</v>
       </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2148,6 +2318,11 @@
       <c r="M35" t="n">
         <v>3.09</v>
       </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2197,6 +2372,11 @@
       <c r="M36" t="n">
         <v>0.98</v>
       </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2246,6 +2426,11 @@
       <c r="M37" t="n">
         <v>2.77</v>
       </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2295,6 +2480,11 @@
       <c r="M38" t="n">
         <v>2.6</v>
       </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2344,6 +2534,11 @@
       <c r="M39" t="n">
         <v>1.99</v>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2393,6 +2588,11 @@
       <c r="M40" t="n">
         <v>4.33</v>
       </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2442,6 +2642,11 @@
       <c r="M41" t="n">
         <v>3.22</v>
       </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2491,6 +2696,11 @@
       <c r="M42" t="n">
         <v>1.91</v>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2540,6 +2750,11 @@
       <c r="M43" t="n">
         <v>0.98</v>
       </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2589,6 +2804,11 @@
       <c r="M44" t="n">
         <v>4.32</v>
       </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2638,6 +2858,11 @@
       <c r="M45" t="n">
         <v>3.43</v>
       </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2687,6 +2912,11 @@
       <c r="M46" t="n">
         <v>3.46</v>
       </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2736,6 +2966,11 @@
       <c r="M47" t="n">
         <v>0.35</v>
       </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2785,6 +3020,11 @@
       <c r="M48" t="n">
         <v>4.27</v>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2834,6 +3074,11 @@
       <c r="M49" t="n">
         <v>1.42</v>
       </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2883,6 +3128,11 @@
       <c r="M50" t="n">
         <v>4.1</v>
       </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2932,6 +3182,11 @@
       <c r="M51" t="n">
         <v>1.25</v>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2981,6 +3236,11 @@
       <c r="M52" t="n">
         <v>1.08</v>
       </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3030,6 +3290,11 @@
       <c r="M53" t="n">
         <v>2.82</v>
       </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3079,6 +3344,11 @@
       <c r="M54" t="n">
         <v>4.26</v>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3128,6 +3398,11 @@
       <c r="M55" t="n">
         <v>1.9</v>
       </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3177,6 +3452,11 @@
       <c r="M56" t="n">
         <v>3.09</v>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3226,6 +3506,11 @@
       <c r="M57" t="n">
         <v>1.25</v>
       </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3275,6 +3560,11 @@
       <c r="M58" t="n">
         <v>2.94</v>
       </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3324,6 +3614,11 @@
       <c r="M59" t="n">
         <v>1.51</v>
       </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3373,6 +3668,11 @@
       <c r="M60" t="n">
         <v>3.77</v>
       </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3422,6 +3722,11 @@
       <c r="M61" t="n">
         <v>4.05</v>
       </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3471,6 +3776,11 @@
       <c r="M62" t="n">
         <v>1.26</v>
       </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3520,6 +3830,11 @@
       <c r="M63" t="n">
         <v>4.43</v>
       </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3569,6 +3884,11 @@
       <c r="M64" t="n">
         <v>2.37</v>
       </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3618,6 +3938,11 @@
       <c r="M65" t="n">
         <v>1.78</v>
       </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3667,6 +3992,11 @@
       <c r="M66" t="n">
         <v>2.18</v>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3716,6 +4046,11 @@
       <c r="M67" t="n">
         <v>4.29</v>
       </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3765,6 +4100,11 @@
       <c r="M68" t="n">
         <v>3.85</v>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3814,6 +4154,11 @@
       <c r="M69" t="n">
         <v>1.68</v>
       </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3863,6 +4208,11 @@
       <c r="M70" t="n">
         <v>0.06</v>
       </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3912,6 +4262,11 @@
       <c r="M71" t="n">
         <v>1.11</v>
       </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3961,6 +4316,11 @@
       <c r="M72" t="n">
         <v>0.42</v>
       </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4010,6 +4370,11 @@
       <c r="M73" t="n">
         <v>1.01</v>
       </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4059,6 +4424,11 @@
       <c r="M74" t="n">
         <v>1.32</v>
       </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4108,6 +4478,11 @@
       <c r="M75" t="n">
         <v>3.09</v>
       </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4157,6 +4532,11 @@
       <c r="M76" t="n">
         <v>2.18</v>
       </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4206,6 +4586,11 @@
       <c r="M77" t="n">
         <v>4.21</v>
       </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4255,6 +4640,11 @@
       <c r="M78" t="n">
         <v>1.62</v>
       </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4304,6 +4694,11 @@
       <c r="M79" t="n">
         <v>0.42</v>
       </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4353,6 +4748,11 @@
       <c r="M80" t="n">
         <v>3.2</v>
       </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4402,6 +4802,11 @@
       <c r="M81" t="n">
         <v>1.86</v>
       </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4451,6 +4856,11 @@
       <c r="M82" t="n">
         <v>3.69</v>
       </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4500,6 +4910,11 @@
       <c r="M83" t="n">
         <v>3.88</v>
       </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4549,6 +4964,11 @@
       <c r="M84" t="n">
         <v>1.87</v>
       </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4598,6 +5018,11 @@
       <c r="M85" t="n">
         <v>3.65</v>
       </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4647,6 +5072,11 @@
       <c r="M86" t="n">
         <v>0.49</v>
       </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4696,6 +5126,11 @@
       <c r="M87" t="n">
         <v>1</v>
       </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4745,6 +5180,11 @@
       <c r="M88" t="n">
         <v>1.62</v>
       </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4794,6 +5234,11 @@
       <c r="M89" t="n">
         <v>0.64</v>
       </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4843,6 +5288,11 @@
       <c r="M90" t="n">
         <v>3.1</v>
       </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4892,6 +5342,11 @@
       <c r="M91" t="n">
         <v>1.22</v>
       </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4941,6 +5396,11 @@
       <c r="M92" t="n">
         <v>3.46</v>
       </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4989,6 +5449,11 @@
       </c>
       <c r="M93" t="n">
         <v>3.07</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>SIMULATED</t>
+        </is>
       </c>
     </row>
   </sheetData>
